--- a/teklif/Akilli_Villa_Gorusme_ve_Teklif.xlsx
+++ b/teklif/Akilli_Villa_Gorusme_ve_Teklif.xlsx
@@ -11,7 +11,8 @@
     <sheet name="Kılavuz" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Görüşme Başlıkları" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Donanım Seçimi" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Ücretlendirme" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Uç Ekipman" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Ücretlendirme" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="406">
   <si>
     <t xml:space="preserve">Akıllı Villa – Müşteri Görüşmesi ve Teklif Çalışma Kitabı</t>
   </si>
@@ -49,6 +50,12 @@
     <t xml:space="preserve">Her alt sistem için Ekonomik / Orta / Premium seçenekleri, protokoller ve tavsiye. Müşterinin bütçe seviyesine göre seçim yapın.</t>
   </si>
   <si>
+    <t xml:space="preserve">Uç Ekipman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vana, selenoid, dedektör ve sensörler: marka seçenekleri, fiyat aralıkları ve örnek miktarlar. Toplamı Ücretlendirme sayfasındaki donanım toplamına otomatik bağlıdır.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ücretlendirme</t>
   </si>
   <si>
@@ -82,6 +89,12 @@
     <t xml:space="preserve">Formül – dokunmayın.</t>
   </si>
   <si>
+    <t xml:space="preserve">Yeşil yazı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Başka sayfadan gelen bağlantı (ör. Uç Ekipman toplamı) – dokunmayın.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ÖNEMLİ</t>
   </si>
   <si>
@@ -592,6 +605,408 @@
     <t xml:space="preserve">Elektrik kesintisinde alarm ve kameralar çalışmaya devam etmeli.</t>
   </si>
   <si>
+    <t xml:space="preserve">Uç Ekipman – Vana, Selenoid, Dedektör ve Sensörler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Örnek 400 m² villa, orta seviye. Fiyatlar adet başına, EUR, KDV hariç, yaklaşık 2026 distribütör tahmini (±%30). Teklif öncesi distribütörden fiyat alın.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ekipman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Önerilen marka / seri (orta seviye)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternatifler (ekonomik → premium)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protokol / çıkış</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Birim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miktar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Birim Fiyat (EUR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tutar (EUR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiyat aralığı (EUR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanalar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elektrotermik vana kafası 24V NC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danfoss TWA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Çin muadili → Möhlenhoff Alpha, Siemens STA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24V aç/kapa (KNX ısıtma aktörü)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 – 45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yerden ısıtma kollektör çıkışı başına 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorlu küresel vana aç/kapa 24V (DN15–25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honeywell, Caleffi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yerli/Unox → Belimo, Siemens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24V aç/kapa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40 – 250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zon, fan-coil, boyler devreleri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorlu oransal vana 0–10V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siemens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESBE → Belimo CCV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0–10V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200 – 450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karışım devresi; Kvs mekanik projeden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana su kesme vanası 1" motorlu küresel, yay geri dönüşlü</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belimo (içme suyu onaylı)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yerli motorlu → Grohe Sense Guard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 – 500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Su baskınında otomatik kesme; solenoid kullanmayın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Su solenoid vanası NC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODE, Danfoss EV220B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tork → Bürkert, Parker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24V / 230V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 – 250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depo dolum vb. kısa süreli kullanım</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sulama vanası 24VAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter PGV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yerli → Rain Bird</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24VAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sulama zonu başına 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doğalgaz selenoid vanası, manuel resetli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tork → Elektrogas, Dungs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dedektörden doğrudan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 – 150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSE/EN 161; gaz şirketi onayı ve yetkili tesisatçı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teknik alarm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaz dedektörü (röle çıkışlı)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teknim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tork, Lorex → Honeywell, Dräger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Röle / kuru kontak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 – 250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mutfak + kazan dairesi; vanayı doğrudan keser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO dedektörü</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lorex → Honeywell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Röle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kazan dairesi, şömine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Su baskın sensörü (nokta tipi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuru kontak prob → Honeywell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuru kontak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 – 60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banyolar, mutfak, teknik hacim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duman dedektörü (konvansiyonel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bosch, Hager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teknim → Gira Dual Q (KNX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 – 180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yatak odaları, koridorlar, teknik hacim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ortam / proses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sıcaklık + nem sensörü (dış ortam / teknik hacim)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thermokon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siemens QFA, MDT (KNX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modbus / 0–10V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 – 200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oda sıcaklıkları KNX tuş takımından alınır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CO₂ / hava kalitesi sensörü</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDT (KNX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thermokon → Siemens QPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 – 350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salon, yatak odası; havalandırma kontrolü</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kapı / pencere manyetik kontak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teknim → Bosch, Honeywell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 – 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alarm + pencere açıkken klimayı kapatma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yağmur / toprak nem sensörü</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter → Rain Bird</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sulama iptali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depo seviye sensörü (hidrostatik)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Şamandıra → Keller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4–20mA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 – 300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Su deposu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basınç transmitteri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danfoss MBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huba → Wika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 – 200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hidrofor / tesisat basıncı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Su / ısı sayacı (M-Bus / Modbus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diehl, Sontex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diehl → Kamstrup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M-Bus / Modbus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 – 300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Şebeke + sıcak su</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Havuz pH / klor ölçüm-dozaj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etatron → Bayrol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modbus / analog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500 – 2.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Havuz varsa miktarı 1 yapın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entegrasyon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KNX binary input 8 kanal (kuru kontaklar için)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDT → ABB, Gira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 – 200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~48 kuru kontak giriş; kontak sayısına göre güncelleyin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24V güç kaynağı (vana ve sensörler)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean Well</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean Well → Phoenix Contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saha klemensi, ara röle, bağlantı aksesuarı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix, Weidmüller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 – 500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UÇ EKİPMAN TOPLAMI (Ücretlendirme sayfasına aktarılır)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not: KNX hareket sensörleri, hava durumu istasyonu ve enerji analizörleri Ücretlendirme sayfasında ayrıca yer alır; burada tekrar sayılmamıştır.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ücretlendirme – Örnek 400 m² Villa (Orta seviye, KNX tabanlı)</t>
   </si>
   <si>
@@ -643,30 +1058,12 @@
     <t xml:space="preserve">Kalem</t>
   </si>
   <si>
-    <t xml:space="preserve">Birim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miktar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Birim Fiyat (EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tutar (EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not</t>
-  </si>
-  <si>
     <t xml:space="preserve">Donanım</t>
   </si>
   <si>
     <t xml:space="preserve">KNX güç kaynağı 640 mA</t>
   </si>
   <si>
-    <t xml:space="preserve">adet</t>
-  </si>
-  <si>
     <t xml:space="preserve">KNX IP router</t>
   </si>
   <si>
@@ -697,10 +1094,10 @@
     <t xml:space="preserve">KNX hareket / doluluk sensörü</t>
   </si>
   <si>
-    <t xml:space="preserve">KNX ısıtma aktörü 6 kanal (+ vana motorları)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yerden ısıtma zonları</t>
+    <t xml:space="preserve">KNX ısıtma aktörü 6 kanal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vana kafaları Uç Ekipman sayfasında</t>
   </si>
   <si>
     <t xml:space="preserve">Klima / VRF gateway</t>
@@ -718,18 +1115,12 @@
     <t xml:space="preserve">Teknik hacim PLC + I/O (havuz, sulama, hidrofor)</t>
   </si>
   <si>
-    <t xml:space="preserve">set</t>
-  </si>
-  <si>
     <t xml:space="preserve">Enerji analizörü (Modbus) + akım trafoları</t>
   </si>
   <si>
     <t xml:space="preserve">Ana + linyeler</t>
   </si>
   <si>
-    <t xml:space="preserve">Gaz / su baskın dedektörü + solenoid vana</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dokunmatik duvar paneli 10"</t>
   </si>
   <si>
@@ -749,6 +1140,12 @@
   </si>
   <si>
     <t xml:space="preserve">Otomasyon panosu (kabin, sigorta, klemens, aksesuar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uç ekipman: vana, selenoid, dedektör, sensör</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uç Ekipman sayfasından otomatik gelir</t>
   </si>
   <si>
     <t xml:space="preserve">Donanım maliyeti toplamı</t>
@@ -853,13 +1250,13 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
-    <numFmt numFmtId="168" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0"/>
     <numFmt numFmtId="169" formatCode="#,##0&quot; ₺&quot;"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -922,6 +1319,13 @@
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1037,7 +1441,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="48">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1082,6 +1486,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1102,7 +1510,31 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1110,15 +1542,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1130,7 +1558,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1138,15 +1570,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1154,35 +1590,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1190,11 +1606,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1450,7 +1886,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -1491,7 +1927,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
@@ -1500,25 +1936,25 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
+      <c r="A8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>10</v>
-      </c>
+      <c r="A9" s="5"/>
       <c r="B9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>12</v>
       </c>
+      <c r="B10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -1526,7 +1962,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -1534,7 +1970,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -1542,31 +1978,47 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>22</v>
-      </c>
+      <c r="A16" s="5"/>
+      <c r="B16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="11" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1598,321 +2050,321 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>32</v>
       </c>
+      <c r="C4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="n">
+      <c r="A5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="15"/>
+      <c r="B5" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="15"/>
+      <c r="B6" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="n">
+      <c r="A7" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="15"/>
+      <c r="F7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="15"/>
+      <c r="B8" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="n">
+      <c r="A9" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="15"/>
+      <c r="B9" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="n">
+      <c r="A10" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="15"/>
+      <c r="B10" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="n">
+      <c r="A11" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="15"/>
+      <c r="B11" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="16"/>
     </row>
     <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="n">
+      <c r="A12" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="16"/>
+    </row>
+    <row r="13" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="15"/>
-    </row>
-    <row r="13" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="F13" s="15"/>
+      <c r="F13" s="16"/>
     </row>
     <row r="14" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="n">
+      <c r="A14" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14" s="15"/>
+      <c r="B14" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="16"/>
     </row>
     <row r="15" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="n">
+      <c r="A15" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="15"/>
+      <c r="B15" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="16"/>
     </row>
     <row r="16" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="n">
+      <c r="A16" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F16" s="15"/>
+      <c r="B16" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="16"/>
     </row>
     <row r="17" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="n">
+      <c r="A17" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="F17" s="15"/>
+      <c r="B17" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" s="16"/>
     </row>
     <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="n">
+      <c r="A18" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" s="15"/>
+      <c r="B18" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="16"/>
     </row>
     <row r="19" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="n">
+      <c r="A19" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" s="15"/>
+      <c r="B19" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="16"/>
     </row>
     <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="n">
+      <c r="A20" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="F20" s="15"/>
+      <c r="B20" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="16"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1950,393 +2402,393 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="F4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>91</v>
       </c>
+      <c r="C4" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="E5" s="14" t="s">
+      <c r="A5" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="B5" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="G5" s="15"/>
+      <c r="C5" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="G5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F6" s="14" t="s">
+      <c r="A6" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="G6" s="15"/>
+      <c r="C6" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="G6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E7" s="14" t="s">
+      <c r="A7" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="B7" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="G7" s="15"/>
+      <c r="C7" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="G7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" s="14" t="s">
+      <c r="A8" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="G9" s="16"/>
+    </row>
+    <row r="10" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="E8" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="G8" s="15"/>
-    </row>
-    <row r="9" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="G9" s="15"/>
-    </row>
-    <row r="10" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="G10" s="15"/>
+      <c r="F10" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="E11" s="14" t="s">
+      <c r="A11" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="B11" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="G11" s="15"/>
+      <c r="C11" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="E12" s="14" t="s">
+      <c r="A12" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="B12" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="G12" s="15"/>
+      <c r="C12" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="G12" s="16"/>
     </row>
     <row r="13" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="E13" s="14" t="s">
+      <c r="A13" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="B13" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="G13" s="15"/>
+      <c r="C13" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="G13" s="16"/>
     </row>
     <row r="14" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="F14" s="14" t="s">
+      <c r="A14" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="G14" s="15"/>
+      <c r="C14" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="G14" s="16"/>
     </row>
     <row r="15" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="E15" s="14" t="s">
+      <c r="A15" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="B15" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="G15" s="15"/>
+      <c r="C15" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="G15" s="16"/>
     </row>
     <row r="16" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="E16" s="14" t="s">
+      <c r="A16" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="B16" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="G16" s="15"/>
+      <c r="C16" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="G16" s="16"/>
     </row>
     <row r="17" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="F17" s="14" t="s">
+      <c r="A17" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="G17" s="15"/>
+      <c r="C17" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="G17" s="16"/>
     </row>
     <row r="18" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="E18" s="14" t="s">
+      <c r="A18" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="B18" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="G18" s="15"/>
+      <c r="C18" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="G18" s="16"/>
     </row>
     <row r="19" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="E19" s="14" t="s">
+      <c r="A19" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="B19" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="G19" s="15"/>
+      <c r="C19" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="G19" s="16"/>
     </row>
     <row r="20" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="E20" s="14" t="s">
+      <c r="A20" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="B20" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="G20" s="15"/>
+      <c r="C20" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="G20" s="16"/>
     </row>
     <row r="21" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="E21" s="14" t="s">
+      <c r="A21" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="B21" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="G21" s="15"/>
+      <c r="C21" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="G21" s="16"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2360,6 +2812,892 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="I5" s="19" t="n">
+        <f aca="false">G5*H5</f>
+        <v>600</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>120</v>
+      </c>
+      <c r="I6" s="19" t="n">
+        <f aca="false">G6*H6</f>
+        <v>480</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>300</v>
+      </c>
+      <c r="I7" s="19" t="n">
+        <f aca="false">G7*H7</f>
+        <v>300</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="I8" s="19" t="n">
+        <f aca="false">G8*H8</f>
+        <v>250</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>90</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <f aca="false">G9*H9</f>
+        <v>90</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <f aca="false">G10*H10</f>
+        <v>180</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>90</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <f aca="false">G11*H11</f>
+        <v>90</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <f aca="false">G12*H12</f>
+        <v>120</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <f aca="false">G13*H13</f>
+        <v>120</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <f aca="false">G14*H14</f>
+        <v>180</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <f aca="false">G15*H15</f>
+        <v>200</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>120</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <f aca="false">G16*H16</f>
+        <v>240</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <f aca="false">G17*H17</f>
+        <v>500</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <f aca="false">G18*H18</f>
+        <v>240</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <f aca="false">G19*H19</f>
+        <v>80</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G20" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="I20" s="19" t="n">
+        <f aca="false">G20*H20</f>
+        <v>200</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G21" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="18" t="n">
+        <v>120</v>
+      </c>
+      <c r="I21" s="19" t="n">
+        <f aca="false">G21*H21</f>
+        <v>120</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="18" t="n">
+        <v>180</v>
+      </c>
+      <c r="I22" s="19" t="n">
+        <f aca="false">G22*H22</f>
+        <v>360</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="18" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I23" s="19" t="n">
+        <f aca="false">G23*H23</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G24" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="I24" s="19" t="n">
+        <f aca="false">G24*H24</f>
+        <v>900</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G25" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="I25" s="19" t="n">
+        <f aca="false">G25*H25</f>
+        <v>120</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="K25" s="15"/>
+    </row>
+    <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="G26" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <f aca="false">G26*H26</f>
+        <v>250</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="K26" s="15"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20"/>
+      <c r="B27" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="22" t="n">
+        <f aca="false">SUM(I5:I26)</f>
+        <v>5620</v>
+      </c>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:G60"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -2374,1099 +3712,1102 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+        <v>327</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
+        <v>328</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
+      <c r="A4" s="24" t="s">
+        <v>329</v>
+      </c>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="B5" s="20" t="n">
+      <c r="A5" s="26" t="s">
+        <v>330</v>
+      </c>
+      <c r="B5" s="27" t="n">
         <v>50</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
+        <v>331</v>
+      </c>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="B6" s="21" t="n">
+      <c r="A6" s="26" t="s">
+        <v>332</v>
+      </c>
+      <c r="B6" s="28" t="n">
         <v>0.25</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
+        <v>333</v>
+      </c>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="B7" s="22" t="n">
+      <c r="A7" s="26" t="s">
+        <v>334</v>
+      </c>
+      <c r="B7" s="29" t="n">
         <v>50</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
+        <v>335</v>
+      </c>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="B8" s="21" t="n">
+      <c r="A8" s="26" t="s">
+        <v>336</v>
+      </c>
+      <c r="B8" s="28" t="n">
         <v>0.1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
+        <v>337</v>
+      </c>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="26" t="s">
+        <v>338</v>
+      </c>
+      <c r="B9" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="26" t="s">
+        <v>340</v>
+      </c>
+      <c r="B10" s="28" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="B9" s="21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D12" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="E12" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="B10" s="21" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="F12" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="B12" s="11" t="s">
+      <c r="G12" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>210</v>
-      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>345</v>
+      </c>
+      <c r="C13" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="B13" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="32" t="n">
         <v>250</v>
       </c>
-      <c r="F13" s="26" t="n">
+      <c r="F13" s="33" t="n">
         <f aca="false">D13*E13</f>
         <v>500</v>
       </c>
-      <c r="G13" s="23"/>
+      <c r="G13" s="30"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="C14" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="B14" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="D14" s="24" t="n">
+      <c r="D14" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="25" t="n">
+      <c r="E14" s="32" t="n">
         <v>450</v>
       </c>
-      <c r="F14" s="26" t="n">
+      <c r="F14" s="33" t="n">
         <f aca="false">D14*E14</f>
         <v>450</v>
       </c>
-      <c r="G14" s="23"/>
+      <c r="G14" s="30"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="C15" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="B15" s="23" t="s">
-        <v>215</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="D15" s="24" t="n">
+      <c r="D15" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="E15" s="25" t="n">
+      <c r="E15" s="32" t="n">
         <v>350</v>
       </c>
-      <c r="F15" s="26" t="n">
+      <c r="F15" s="33" t="n">
         <f aca="false">D15*E15</f>
         <v>2100</v>
       </c>
-      <c r="G15" s="23" t="s">
-        <v>216</v>
+      <c r="G15" s="30" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>349</v>
+      </c>
+      <c r="C16" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="B16" s="23" t="s">
-        <v>217</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="D16" s="24" t="n">
+      <c r="D16" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="E16" s="25" t="n">
+      <c r="E16" s="32" t="n">
         <v>450</v>
       </c>
-      <c r="F16" s="26" t="n">
+      <c r="F16" s="33" t="n">
         <f aca="false">D16*E16</f>
         <v>1800</v>
       </c>
-      <c r="G16" s="23" t="s">
-        <v>218</v>
+      <c r="G16" s="30" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>351</v>
+      </c>
+      <c r="C17" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="B17" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="D17" s="24" t="n">
+      <c r="D17" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="E17" s="25" t="n">
+      <c r="E17" s="32" t="n">
         <v>350</v>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="33" t="n">
         <f aca="false">D17*E17</f>
         <v>1400</v>
       </c>
-      <c r="G17" s="23" t="s">
-        <v>220</v>
+      <c r="G17" s="30" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>353</v>
+      </c>
+      <c r="C18" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="B18" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="D18" s="24" t="n">
+      <c r="D18" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="E18" s="25" t="n">
+      <c r="E18" s="32" t="n">
         <v>250</v>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="33" t="n">
         <f aca="false">D18*E18</f>
         <v>3500</v>
       </c>
-      <c r="G18" s="23" t="s">
-        <v>222</v>
+      <c r="G18" s="30" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>355</v>
+      </c>
+      <c r="C19" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="B19" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="D19" s="24" t="n">
+      <c r="D19" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="E19" s="25" t="n">
+      <c r="E19" s="32" t="n">
         <v>150</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="33" t="n">
         <f aca="false">D19*E19</f>
         <v>1500</v>
       </c>
-      <c r="G19" s="23"/>
+      <c r="G19" s="30"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="C20" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="B20" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="D20" s="24" t="n">
+      <c r="D20" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="E20" s="25" t="n">
+      <c r="E20" s="32" t="n">
         <v>450</v>
       </c>
-      <c r="F20" s="26" t="n">
+      <c r="F20" s="33" t="n">
         <f aca="false">D20*E20</f>
         <v>1350</v>
       </c>
-      <c r="G20" s="23" t="s">
-        <v>225</v>
+      <c r="G20" s="30" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>358</v>
+      </c>
+      <c r="C21" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="B21" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="D21" s="24" t="n">
+      <c r="D21" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="25" t="n">
+      <c r="E21" s="32" t="n">
         <v>700</v>
       </c>
-      <c r="F21" s="26" t="n">
+      <c r="F21" s="33" t="n">
         <f aca="false">D21*E21</f>
         <v>700</v>
       </c>
-      <c r="G21" s="23" t="s">
-        <v>227</v>
+      <c r="G21" s="30" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>360</v>
+      </c>
+      <c r="C22" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="B22" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="D22" s="24" t="n">
+      <c r="D22" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="25" t="n">
+      <c r="E22" s="32" t="n">
         <v>600</v>
       </c>
-      <c r="F22" s="26" t="n">
+      <c r="F22" s="33" t="n">
         <f aca="false">D22*E22</f>
         <v>600</v>
       </c>
-      <c r="G22" s="23" t="s">
-        <v>229</v>
+      <c r="G22" s="30" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="D23" s="24" t="n">
+      <c r="A23" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>362</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="D23" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="25" t="n">
+      <c r="E23" s="32" t="n">
         <v>1500</v>
       </c>
-      <c r="F23" s="26" t="n">
+      <c r="F23" s="33" t="n">
         <f aca="false">D23*E23</f>
         <v>1500</v>
       </c>
-      <c r="G23" s="23"/>
+      <c r="G23" s="30"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>363</v>
+      </c>
+      <c r="C24" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="B24" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="D24" s="24" t="n">
+      <c r="D24" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="E24" s="25" t="n">
+      <c r="E24" s="32" t="n">
         <v>200</v>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F24" s="33" t="n">
         <f aca="false">D24*E24</f>
         <v>800</v>
       </c>
-      <c r="G24" s="23" t="s">
-        <v>233</v>
+      <c r="G24" s="30" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B25" s="30" t="s">
+        <v>365</v>
+      </c>
+      <c r="C25" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="B25" s="23" t="s">
-        <v>234</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="D25" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="E25" s="25" t="n">
-        <v>280</v>
-      </c>
-      <c r="F25" s="26" t="n">
+      <c r="D25" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="32" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F25" s="33" t="n">
         <f aca="false">D25*E25</f>
-        <v>840</v>
-      </c>
-      <c r="G25" s="23"/>
+        <v>2400</v>
+      </c>
+      <c r="G25" s="30"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="23" t="s">
+      <c r="A26" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B26" s="30" t="s">
+        <v>366</v>
+      </c>
+      <c r="C26" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="B26" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="D26" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" s="25" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F26" s="26" t="n">
+      <c r="D26" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="32" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F26" s="33" t="n">
         <f aca="false">D26*E26</f>
-        <v>2400</v>
-      </c>
-      <c r="G26" s="23"/>
+        <v>1500</v>
+      </c>
+      <c r="G26" s="30"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>367</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="D27" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="34" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F27" s="33" t="n">
+        <f aca="false">D27*E27</f>
+        <v>2000</v>
+      </c>
+      <c r="G27" s="30" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>369</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="D28" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="32" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F28" s="33" t="n">
+        <f aca="false">D28*E28</f>
+        <v>1800</v>
+      </c>
+      <c r="G28" s="30"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B29" s="30" t="s">
+        <v>370</v>
+      </c>
+      <c r="C29" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="B27" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="D27" s="24" t="n">
+      <c r="D29" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="25" t="n">
+      <c r="E29" s="32" t="n">
+        <v>700</v>
+      </c>
+      <c r="F29" s="33" t="n">
+        <f aca="false">D29*E29</f>
+        <v>700</v>
+      </c>
+      <c r="G29" s="30"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B30" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="D30" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="32" t="n">
         <v>1500</v>
       </c>
-      <c r="F27" s="26" t="n">
-        <f aca="false">D27*E27</f>
+      <c r="F30" s="33" t="n">
+        <f aca="false">D30*E30</f>
         <v>1500</v>
       </c>
-      <c r="G27" s="23"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="D28" s="24" t="n">
+      <c r="G30" s="30"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B31" s="30" t="s">
+        <v>372</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="D31" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="27" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F28" s="26" t="n">
-        <f aca="false">D28*E28</f>
-        <v>2000</v>
-      </c>
-      <c r="G28" s="23" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="D29" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="25" t="n">
-        <v>1800</v>
-      </c>
-      <c r="F29" s="26" t="n">
-        <f aca="false">D29*E29</f>
-        <v>1800</v>
-      </c>
-      <c r="G29" s="23"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="D30" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="25" t="n">
-        <v>700</v>
-      </c>
-      <c r="F30" s="26" t="n">
-        <f aca="false">D30*E30</f>
-        <v>700</v>
-      </c>
-      <c r="G30" s="23"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>241</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="D31" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="25" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F31" s="26" t="n">
+      <c r="E31" s="35" t="n">
+        <f aca="false">'Uç Ekipman'!I27</f>
+        <v>5620</v>
+      </c>
+      <c r="F31" s="33" t="n">
         <f aca="false">D31*E31</f>
-        <v>1500</v>
-      </c>
-      <c r="G31" s="23"/>
+        <v>5620</v>
+      </c>
+      <c r="G31" s="30" t="s">
+        <v>373</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="23"/>
-      <c r="B32" s="28" t="s">
-        <v>242</v>
-      </c>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="29" t="n">
+      <c r="A32" s="30"/>
+      <c r="B32" s="36" t="s">
+        <v>374</v>
+      </c>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="37" t="n">
         <f aca="false">SUM(F13:F31)</f>
-        <v>26940</v>
-      </c>
-      <c r="G32" s="23"/>
+        <v>31720</v>
+      </c>
+      <c r="G32" s="30"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="23"/>
-      <c r="B33" s="28" t="s">
-        <v>243</v>
-      </c>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="29" t="n">
+      <c r="A33" s="30"/>
+      <c r="B33" s="36" t="s">
+        <v>375</v>
+      </c>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="37" t="n">
         <f aca="false">F32*(1+$B$6)</f>
-        <v>33675</v>
-      </c>
-      <c r="G33" s="23"/>
+        <v>39650</v>
+      </c>
+      <c r="G33" s="30"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="23"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="23"/>
+      <c r="A34" s="30"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="30"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="B35" s="11" t="s">
+      <c r="A35" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="E35" s="38" t="s">
+        <v>377</v>
+      </c>
+      <c r="F35" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="G35" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="C35" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="E35" s="30" t="s">
-        <v>245</v>
-      </c>
-      <c r="F35" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>210</v>
-      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="B36" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="D36" s="24" t="n">
+      <c r="A36" s="30" t="s">
+        <v>378</v>
+      </c>
+      <c r="B36" s="30" t="s">
+        <v>379</v>
+      </c>
+      <c r="C36" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="D36" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="E36" s="31" t="n">
+      <c r="E36" s="39" t="n">
         <f aca="false">$B$7</f>
         <v>50</v>
       </c>
-      <c r="F36" s="26" t="n">
+      <c r="F36" s="33" t="n">
         <f aca="false">D36*E36</f>
         <v>800</v>
       </c>
-      <c r="G36" s="23"/>
+      <c r="G36" s="30"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="B37" s="23" t="s">
-        <v>249</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="D37" s="24" t="n">
+      <c r="A37" s="30" t="s">
+        <v>378</v>
+      </c>
+      <c r="B37" s="30" t="s">
+        <v>381</v>
+      </c>
+      <c r="C37" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="D37" s="31" t="n">
         <v>24</v>
       </c>
-      <c r="E37" s="31" t="n">
+      <c r="E37" s="39" t="n">
         <f aca="false">$B$7</f>
         <v>50</v>
       </c>
-      <c r="F37" s="26" t="n">
+      <c r="F37" s="33" t="n">
         <f aca="false">D37*E37</f>
         <v>1200</v>
       </c>
-      <c r="G37" s="23"/>
+      <c r="G37" s="30"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="B38" s="23" t="s">
-        <v>250</v>
-      </c>
-      <c r="C38" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="D38" s="24" t="n">
+      <c r="A38" s="30" t="s">
+        <v>378</v>
+      </c>
+      <c r="B38" s="30" t="s">
+        <v>382</v>
+      </c>
+      <c r="C38" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="D38" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="E38" s="31" t="n">
+      <c r="E38" s="39" t="n">
         <f aca="false">$B$7</f>
         <v>50</v>
       </c>
-      <c r="F38" s="26" t="n">
+      <c r="F38" s="33" t="n">
         <f aca="false">D38*E38</f>
         <v>2000</v>
       </c>
-      <c r="G38" s="23"/>
+      <c r="G38" s="30"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="B39" s="23" t="s">
-        <v>251</v>
-      </c>
-      <c r="C39" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="D39" s="24" t="n">
+      <c r="A39" s="30" t="s">
+        <v>378</v>
+      </c>
+      <c r="B39" s="30" t="s">
+        <v>383</v>
+      </c>
+      <c r="C39" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="D39" s="31" t="n">
         <v>60</v>
       </c>
-      <c r="E39" s="31" t="n">
+      <c r="E39" s="39" t="n">
         <f aca="false">$B$7</f>
         <v>50</v>
       </c>
-      <c r="F39" s="26" t="n">
+      <c r="F39" s="33" t="n">
         <f aca="false">D39*E39</f>
         <v>3000</v>
       </c>
-      <c r="G39" s="23"/>
+      <c r="G39" s="30"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="B40" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="C40" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="D40" s="24" t="n">
+      <c r="A40" s="30" t="s">
+        <v>378</v>
+      </c>
+      <c r="B40" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="C40" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="D40" s="31" t="n">
         <v>60</v>
       </c>
-      <c r="E40" s="31" t="n">
+      <c r="E40" s="39" t="n">
         <f aca="false">$B$7</f>
         <v>50</v>
       </c>
-      <c r="F40" s="26" t="n">
+      <c r="F40" s="33" t="n">
         <f aca="false">D40*E40</f>
         <v>3000</v>
       </c>
-      <c r="G40" s="23" t="s">
-        <v>253</v>
+      <c r="G40" s="30" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="B41" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="C41" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="D41" s="24" t="n">
+      <c r="A41" s="30" t="s">
+        <v>378</v>
+      </c>
+      <c r="B41" s="30" t="s">
+        <v>386</v>
+      </c>
+      <c r="C41" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="D41" s="31" t="n">
         <v>24</v>
       </c>
-      <c r="E41" s="31" t="n">
+      <c r="E41" s="39" t="n">
         <f aca="false">$B$7</f>
         <v>50</v>
       </c>
-      <c r="F41" s="26" t="n">
+      <c r="F41" s="33" t="n">
         <f aca="false">D41*E41</f>
         <v>1200</v>
       </c>
-      <c r="G41" s="23"/>
+      <c r="G41" s="30"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="B42" s="23" t="s">
-        <v>255</v>
-      </c>
-      <c r="C42" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="D42" s="24" t="n">
+      <c r="A42" s="30" t="s">
+        <v>378</v>
+      </c>
+      <c r="B42" s="30" t="s">
+        <v>387</v>
+      </c>
+      <c r="C42" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="D42" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="E42" s="31" t="n">
+      <c r="E42" s="39" t="n">
         <f aca="false">$B$7</f>
         <v>50</v>
       </c>
-      <c r="F42" s="26" t="n">
+      <c r="F42" s="33" t="n">
         <f aca="false">D42*E42</f>
         <v>2000</v>
       </c>
-      <c r="G42" s="23"/>
+      <c r="G42" s="30"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="B43" s="23" t="s">
-        <v>256</v>
-      </c>
-      <c r="C43" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="D43" s="24" t="n">
+      <c r="A43" s="30" t="s">
+        <v>378</v>
+      </c>
+      <c r="B43" s="30" t="s">
+        <v>388</v>
+      </c>
+      <c r="C43" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="D43" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="E43" s="31" t="n">
+      <c r="E43" s="39" t="n">
         <f aca="false">$B$7</f>
         <v>50</v>
       </c>
-      <c r="F43" s="26" t="n">
+      <c r="F43" s="33" t="n">
         <f aca="false">D43*E43</f>
         <v>800</v>
       </c>
-      <c r="G43" s="23" t="s">
-        <v>257</v>
+      <c r="G43" s="30" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="23"/>
-      <c r="B44" s="28" t="s">
-        <v>258</v>
-      </c>
-      <c r="C44" s="23"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="29" t="n">
+      <c r="A44" s="30"/>
+      <c r="B44" s="36" t="s">
+        <v>390</v>
+      </c>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="33"/>
+      <c r="F44" s="37" t="n">
         <f aca="false">SUM(F36:F43)</f>
         <v>14000</v>
       </c>
-      <c r="G44" s="23"/>
+      <c r="G44" s="30"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="23"/>
-      <c r="B45" s="23"/>
-      <c r="C45" s="23"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="26"/>
-      <c r="G45" s="23"/>
+      <c r="A45" s="30"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="33"/>
+      <c r="F45" s="33"/>
+      <c r="G45" s="30"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="B46" s="11" t="s">
+      <c r="A46" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="E46" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="F46" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="G46" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="C46" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="E46" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="F46" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="G46" s="11" t="s">
-        <v>210</v>
-      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="B47" s="23" t="s">
-        <v>260</v>
-      </c>
-      <c r="C47" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="D47" s="24" t="n">
+      <c r="A47" s="30" t="s">
+        <v>391</v>
+      </c>
+      <c r="B47" s="30" t="s">
+        <v>392</v>
+      </c>
+      <c r="C47" s="30" t="s">
+        <v>393</v>
+      </c>
+      <c r="D47" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="E47" s="25" t="n">
+      <c r="E47" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="F47" s="26" t="n">
+      <c r="F47" s="33" t="n">
         <f aca="false">D47*E47</f>
         <v>0</v>
       </c>
-      <c r="G47" s="23" t="s">
-        <v>262</v>
+      <c r="G47" s="30" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="32"/>
-      <c r="B48" s="32"/>
-      <c r="C48" s="32"/>
-      <c r="D48" s="32"/>
-      <c r="E48" s="33"/>
-      <c r="F48" s="33"/>
-      <c r="G48" s="32"/>
+      <c r="A48" s="40"/>
+      <c r="B48" s="40"/>
+      <c r="C48" s="40"/>
+      <c r="D48" s="40"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="41"/>
+      <c r="G48" s="40"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="17" t="s">
-        <v>263</v>
-      </c>
-      <c r="B49" s="34"/>
-      <c r="C49" s="34"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="35"/>
-      <c r="F49" s="35"/>
-      <c r="G49" s="34"/>
+      <c r="A49" s="24" t="s">
+        <v>395</v>
+      </c>
+      <c r="B49" s="42"/>
+      <c r="C49" s="42"/>
+      <c r="D49" s="42"/>
+      <c r="E49" s="43"/>
+      <c r="F49" s="43"/>
+      <c r="G49" s="42"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="32"/>
-      <c r="B50" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="C50" s="32"/>
-      <c r="D50" s="32"/>
-      <c r="E50" s="33"/>
-      <c r="F50" s="33" t="n">
+      <c r="A50" s="40"/>
+      <c r="B50" s="40" t="s">
+        <v>396</v>
+      </c>
+      <c r="C50" s="40"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="41" t="n">
         <f aca="false">F33</f>
-        <v>33675</v>
-      </c>
-      <c r="G50" s="32"/>
+        <v>39650</v>
+      </c>
+      <c r="G50" s="40"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="32"/>
-      <c r="B51" s="32" t="s">
-        <v>246</v>
-      </c>
-      <c r="C51" s="32"/>
-      <c r="D51" s="32"/>
-      <c r="E51" s="33"/>
-      <c r="F51" s="33" t="n">
+      <c r="A51" s="40"/>
+      <c r="B51" s="40" t="s">
+        <v>378</v>
+      </c>
+      <c r="C51" s="40"/>
+      <c r="D51" s="40"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="41" t="n">
         <f aca="false">F44</f>
         <v>14000</v>
       </c>
-      <c r="G51" s="32"/>
+      <c r="G51" s="40"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="32"/>
-      <c r="B52" s="32" t="s">
-        <v>265</v>
-      </c>
-      <c r="C52" s="32"/>
-      <c r="D52" s="32"/>
-      <c r="E52" s="33"/>
-      <c r="F52" s="33" t="n">
+      <c r="A52" s="40"/>
+      <c r="B52" s="40" t="s">
+        <v>397</v>
+      </c>
+      <c r="C52" s="40"/>
+      <c r="D52" s="40"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="41" t="n">
         <f aca="false">F47</f>
         <v>0</v>
       </c>
-      <c r="G52" s="32"/>
+      <c r="G52" s="40"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="32"/>
-      <c r="B53" s="32" t="s">
-        <v>198</v>
-      </c>
-      <c r="C53" s="32"/>
-      <c r="D53" s="32"/>
-      <c r="E53" s="33"/>
-      <c r="F53" s="33" t="n">
+      <c r="A53" s="40"/>
+      <c r="B53" s="40" t="s">
+        <v>336</v>
+      </c>
+      <c r="C53" s="40"/>
+      <c r="D53" s="40"/>
+      <c r="E53" s="41"/>
+      <c r="F53" s="41" t="n">
         <f aca="false">SUM(F50:F52)*$B$8</f>
-        <v>4767.5</v>
-      </c>
-      <c r="G53" s="32"/>
+        <v>5365</v>
+      </c>
+      <c r="G53" s="40"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="32"/>
+      <c r="A54" s="40"/>
       <c r="B54" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="C54" s="32"/>
-      <c r="D54" s="32"/>
-      <c r="E54" s="33"/>
-      <c r="F54" s="36" t="n">
+        <v>398</v>
+      </c>
+      <c r="C54" s="40"/>
+      <c r="D54" s="40"/>
+      <c r="E54" s="41"/>
+      <c r="F54" s="44" t="n">
         <f aca="false">SUM(F50:F53)</f>
-        <v>52442.5</v>
-      </c>
-      <c r="G54" s="32"/>
+        <v>59015</v>
+      </c>
+      <c r="G54" s="40"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="32"/>
-      <c r="B55" s="32" t="s">
-        <v>267</v>
-      </c>
-      <c r="C55" s="32"/>
-      <c r="D55" s="32"/>
-      <c r="E55" s="33"/>
-      <c r="F55" s="33" t="n">
+      <c r="A55" s="40"/>
+      <c r="B55" s="40" t="s">
+        <v>399</v>
+      </c>
+      <c r="C55" s="40"/>
+      <c r="D55" s="40"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="41" t="n">
         <f aca="false">F54*$B$9</f>
-        <v>10488.5</v>
-      </c>
-      <c r="G55" s="32"/>
+        <v>11803</v>
+      </c>
+      <c r="G55" s="40"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="32"/>
-      <c r="B56" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="C56" s="32"/>
-      <c r="D56" s="32"/>
-      <c r="E56" s="33"/>
-      <c r="F56" s="38" t="n">
+      <c r="A56" s="40"/>
+      <c r="B56" s="45" t="s">
+        <v>400</v>
+      </c>
+      <c r="C56" s="40"/>
+      <c r="D56" s="40"/>
+      <c r="E56" s="41"/>
+      <c r="F56" s="46" t="n">
         <f aca="false">F54+F55</f>
-        <v>62931</v>
-      </c>
-      <c r="G56" s="32"/>
+        <v>70818</v>
+      </c>
+      <c r="G56" s="40"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="32"/>
-      <c r="B57" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="C57" s="32"/>
-      <c r="D57" s="32"/>
-      <c r="E57" s="33"/>
-      <c r="F57" s="39" t="n">
+      <c r="A57" s="40"/>
+      <c r="B57" s="45" t="s">
+        <v>401</v>
+      </c>
+      <c r="C57" s="40"/>
+      <c r="D57" s="40"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="47" t="n">
         <f aca="false">F56*$B$5</f>
-        <v>3146550</v>
-      </c>
-      <c r="G57" s="32"/>
+        <v>3540900</v>
+      </c>
+      <c r="G57" s="40"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="32"/>
-      <c r="B58" s="32" t="s">
-        <v>270</v>
-      </c>
-      <c r="C58" s="32" t="s">
-        <v>271</v>
+      <c r="A58" s="40"/>
+      <c r="B58" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="C58" s="40" t="s">
+        <v>403</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>400</v>
       </c>
-      <c r="E58" s="33"/>
-      <c r="F58" s="33" t="n">
+      <c r="E58" s="41"/>
+      <c r="F58" s="41" t="n">
         <f aca="false">IF(D58&gt;0,F54/D58,0)</f>
-        <v>131.10625</v>
-      </c>
-      <c r="G58" s="32"/>
+        <v>147.5375</v>
+      </c>
+      <c r="G58" s="40"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="32"/>
-      <c r="B59" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="C59" s="32"/>
-      <c r="D59" s="32"/>
-      <c r="E59" s="33"/>
-      <c r="F59" s="33" t="n">
+      <c r="A59" s="40"/>
+      <c r="B59" s="40" t="s">
+        <v>404</v>
+      </c>
+      <c r="C59" s="40"/>
+      <c r="D59" s="40"/>
+      <c r="E59" s="41"/>
+      <c r="F59" s="41" t="n">
         <f aca="false">F33-F32+F44</f>
-        <v>20735</v>
-      </c>
-      <c r="G59" s="32"/>
+        <v>21930</v>
+      </c>
+      <c r="G59" s="40"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="32"/>
-      <c r="B60" s="32" t="s">
-        <v>273</v>
-      </c>
-      <c r="C60" s="32"/>
-      <c r="D60" s="32"/>
-      <c r="E60" s="33"/>
-      <c r="F60" s="33" t="n">
+      <c r="A60" s="40"/>
+      <c r="B60" s="40" t="s">
+        <v>405</v>
+      </c>
+      <c r="C60" s="40"/>
+      <c r="D60" s="40"/>
+      <c r="E60" s="41"/>
+      <c r="F60" s="41" t="n">
         <f aca="false">F54*$B$10</f>
-        <v>4195.4</v>
-      </c>
-      <c r="G60" s="32"/>
+        <v>4721.2</v>
+      </c>
+      <c r="G60" s="40"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
